--- a/ig/DM-SIDOBA/ValueSet-JDV-J264-ModeEtCentreDePriseEnCharge-MDPH.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-JDV-J264-ModeEtCentreDePriseEnCharge-MDPH.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,6 +117,12 @@
     <t>Accueil de nuit</t>
   </si>
   <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Sur les lieux de vie</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -125,15 +130,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R213-ModePriseEnCharge/FHIR/TRE-R213-ModePriseEnCharge</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
   </si>
 </sst>
 </file>
@@ -395,7 +391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -439,61 +435,23 @@
         <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>36</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
+    <row r="7">
+      <c r="A7" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="B7" t="s" s="2">
         <v>38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
